--- a/doc/MAPS_TEST.xlsx
+++ b/doc/MAPS_TEST.xlsx
@@ -4,20 +4,21 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="600" windowWidth="9375" windowHeight="13725" activeTab="2"/>
+    <workbookView xWindow="390" yWindow="600" windowWidth="9375" windowHeight="13725" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="class" sheetId="3" r:id="rId1"/>
     <sheet name="class_d1" sheetId="4" r:id="rId2"/>
     <sheet name="members" sheetId="2" r:id="rId3"/>
     <sheet name="number_class_details" sheetId="5" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="349">
   <si>
     <t>member_id</t>
   </si>
@@ -230,11 +231,11 @@
   </si>
   <si>
     <t>class_loc</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>class_week</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -250,81 +251,81 @@
       </rPr>
       <t>lass_loop</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>부산단기투자클럽A</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>부산</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>class_time_to</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>class_time_from</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>월</t>
   </si>
   <si>
     <t>월</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>class_loop_kijun</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>PT</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>일반</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>단체</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>1:1</t>
   </si>
   <si>
     <t>1:1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>2:1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>3:1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>4:1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>class_price</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>class_loop_mim</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>guaranteed_type</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>guaranteed_details</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -339,11 +340,11 @@
       </rPr>
       <t>1</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>5001_20260128121033_2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -512,42 +513,42 @@
   </si>
   <si>
     <t>class_date</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>reg_id</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>number_class_details_id</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>name3</t>
   </si>
   <si>
     <t>CLASS</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>remark</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>PT</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>class_grade</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>class_type</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>class_loop</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -571,7 +572,7 @@
       </rPr>
       <t>A</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -585,7 +586,7 @@
       </rPr>
       <t>일반</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -599,7 +600,7 @@
       </rPr>
       <t>부산</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -613,7 +614,7 @@
       </rPr>
       <t>물건추천</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -627,7 +628,7 @@
       </rPr>
       <t>입찰가</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -651,7 +652,7 @@
       </rPr>
       <t>B</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -665,7 +666,7 @@
       </rPr>
       <t>수</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -689,7 +690,7 @@
       </rPr>
       <t>A</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -703,7 +704,7 @@
       </rPr>
       <t>서울</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -717,7 +718,7 @@
       </rPr>
       <t>토</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -731,7 +732,7 @@
       </rPr>
       <t>온라인단기투자클럽</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -745,7 +746,7 @@
       </rPr>
       <t>온라인</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -759,7 +760,7 @@
       </rPr>
       <t>금</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -773,7 +774,7 @@
       </rPr>
       <t>낙찰</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -787,7 +788,7 @@
       </rPr>
       <t>일반</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -801,7 +802,7 @@
       </rPr>
       <t>온라인추천물건</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -815,7 +816,7 @@
       </rPr>
       <t>낙찰</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -829,7 +830,7 @@
       </rPr>
       <t>서울</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -843,7 +844,7 @@
       </rPr>
       <t>부산</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -857,7 +858,7 @@
       </rPr>
       <t>플레티넘</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -871,7 +872,7 @@
       </rPr>
       <t>수익</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -885,7 +886,7 @@
       </rPr>
       <t>블랙</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -899,7 +900,7 @@
       </rPr>
       <t>실버</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -913,7 +914,7 @@
       </rPr>
       <t>블루존</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -927,11 +928,11 @@
       </rPr>
       <t>온라인</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>수업</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -948,7 +949,7 @@
       </rPr>
       <t>달</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -965,7 +966,7 @@
       </rPr>
       <t>달</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -982,7 +983,7 @@
       </rPr>
       <t>건</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1002,27 +1003,27 @@
   </si>
   <si>
     <t>수업</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>온라인트레이닝반</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>온라인경매초급반</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>수</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>격주</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>겨주</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1046,7 +1047,7 @@
       </rPr>
       <t xml:space="preserve"> PT</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>member_token</t>
@@ -1062,26 +1063,26 @@
   </si>
   <si>
     <t>class_id</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>account_bank</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>account_name</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>name1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>name2</t>
   </si>
   <si>
     <t>member_name</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>곽지혜</t>
@@ -1535,7 +1536,7 @@
   </si>
   <si>
     <t>대구</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1554,7 +1555,7 @@
   </si>
   <si>
     <t>개인,법인</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>class_type</t>
@@ -1567,23 +1568,23 @@
   </si>
   <si>
     <t>class_d1_id</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>gubun</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>회원</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>관리자</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>이정우</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1599,27 +1600,107 @@
       </rPr>
       <t>10-4238-7781</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>name1_gubun</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>name2_gubun</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>name3_gubun</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>reg_id</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>kaib_date</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>조사물건관리</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>입찰일자</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>사건번호</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>법원</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>담당</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>조사자</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>조사자 회원등록 및 텔레그램 등록</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>텔레그램전송</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>조사요청</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>체크박스</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>메뉴명</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>상태</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>조사</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>조사 선택시 옥션 물건 조회창 새로 고침</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>신규</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>요청</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>폐기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>전달완료</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>등록완료</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>입찰물건관리 상품등록</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1629,13 +1710,21 @@
   <numFmts count="3">
     <numFmt numFmtId="42" formatCode="_-&quot;₩&quot;* #,##0_-;\-&quot;₩&quot;* #,##0_-;_-&quot;₩&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="#,##0_ "/>
+    <numFmt numFmtId="176" formatCode="#,##0_ "/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1925,3554 +2014,3555 @@
   </borders>
   <cellStyleXfs count="1136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="15" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="389" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="2" xfId="368" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="389" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="2" xfId="368" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="368" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="368" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="368" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="368" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="576" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="576" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="576" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="576" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="389" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="389" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="25" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="368" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="368" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="389" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="3" xfId="368" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="389" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="3" xfId="368" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1136">
     <cellStyle name="메모 2" xfId="9"/>
@@ -8284,7 +8374,7 @@
   <sortState ref="A2:J9">
     <sortCondition sortBy="fontColor" ref="A6" dxfId="0"/>
   </sortState>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="42" orientation="landscape" r:id="rId1"/>
   <colBreaks count="1" manualBreakCount="1">
@@ -8907,7 +8997,7 @@
       <c r="O14" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -12730,7 +12820,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -12765,7 +12855,105 @@
       <c r="C2" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="G9:R17"/>
+  <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="6" width="9.140625" style="53"/>
+    <col min="7" max="7" width="17.7109375" style="53" customWidth="1"/>
+    <col min="8" max="9" width="9.140625" style="53"/>
+    <col min="10" max="10" width="13.140625" style="53" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" style="53" customWidth="1"/>
+    <col min="12" max="17" width="9.140625" style="53"/>
+    <col min="18" max="18" width="33.140625" style="53" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="53"/>
+  </cols>
+  <sheetData>
+    <row r="9" spans="7:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J9" s="53" t="s">
+        <v>337</v>
+      </c>
+      <c r="K9" s="53" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="11" spans="7:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G11" s="53" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="12" spans="7:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G12" s="53" t="s">
+        <v>329</v>
+      </c>
+      <c r="J12" s="53" t="s">
+        <v>338</v>
+      </c>
+      <c r="K12" s="53" t="s">
+        <v>330</v>
+      </c>
+      <c r="L12" s="53" t="s">
+        <v>331</v>
+      </c>
+      <c r="M12" s="53" t="s">
+        <v>332</v>
+      </c>
+      <c r="O12" s="53" t="s">
+        <v>340</v>
+      </c>
+      <c r="P12" s="53" t="s">
+        <v>333</v>
+      </c>
+      <c r="Q12" s="53" t="s">
+        <v>334</v>
+      </c>
+      <c r="R12" s="53" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="13" spans="7:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N13" s="53" t="s">
+        <v>343</v>
+      </c>
+      <c r="O13" s="53" t="s">
+        <v>341</v>
+      </c>
+      <c r="R13" s="53" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="14" spans="7:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N14" s="53" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="15" spans="7:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N15" s="53" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="16" spans="7:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N16" s="53" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="17" spans="14:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N17" s="53" t="s">
+        <v>347</v>
+      </c>
+      <c r="R17" s="53" t="s">
+        <v>348</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/doc/MAPS_TEST.xlsx
+++ b/doc/MAPS_TEST.xlsx
@@ -4,21 +4,22 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="600" windowWidth="9375" windowHeight="13725" activeTab="4"/>
+    <workbookView xWindow="390" yWindow="600" windowWidth="9375" windowHeight="13725" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="class" sheetId="3" r:id="rId1"/>
     <sheet name="class_d1" sheetId="4" r:id="rId2"/>
     <sheet name="members" sheetId="2" r:id="rId3"/>
     <sheet name="number_class_details" sheetId="5" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="6" r:id="rId5"/>
+    <sheet name="조사메뉴" sheetId="6" r:id="rId5"/>
+    <sheet name="회원취소건" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="370">
   <si>
     <t>member_id</t>
   </si>
@@ -1702,17 +1703,130 @@
     <t>입찰물건관리 상품등록</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
+  <si>
+    <t>추천</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>입찰</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>취소</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>합계</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>변경</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>26-03</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>26-02</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>26-01</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>날자</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추천</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>입찰</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>취소</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>변경</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>* 요약</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>* 리스트</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>일자</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>입찰일자</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>사건번호</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>법원</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>비고</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_-&quot;₩&quot;* #,##0_-;\-&quot;₩&quot;* #,##0_-;_-&quot;₩&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="#,##0_ "/>
+    <numFmt numFmtId="177" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1917,8 +2031,17 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1958,6 +2081,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5412,7 +5541,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -5563,6 +5692,28 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1136">
     <cellStyle name="메모 2" xfId="9"/>
@@ -12956,4 +13107,189 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="D3:J16"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="F3" s="54" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="4" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="F4" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="G4" s="4">
+        <v>20</v>
+      </c>
+      <c r="H4" s="4">
+        <v>5</v>
+      </c>
+      <c r="I4" s="4">
+        <v>6</v>
+      </c>
+      <c r="J4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="E5" s="55"/>
+      <c r="F5" s="60" t="s">
+        <v>358</v>
+      </c>
+      <c r="G5" s="60" t="s">
+        <v>359</v>
+      </c>
+      <c r="H5" s="60" t="s">
+        <v>360</v>
+      </c>
+      <c r="I5" s="60" t="s">
+        <v>361</v>
+      </c>
+      <c r="J5" s="60" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="6" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D6" s="54"/>
+      <c r="F6" s="57" t="s">
+        <v>354</v>
+      </c>
+      <c r="G6" s="4">
+        <v>15</v>
+      </c>
+      <c r="H6" s="4">
+        <v>3</v>
+      </c>
+      <c r="I6" s="4">
+        <v>4</v>
+      </c>
+      <c r="J6" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="F7" s="57" t="s">
+        <v>355</v>
+      </c>
+      <c r="G7" s="4">
+        <v>5</v>
+      </c>
+      <c r="H7" s="4">
+        <v>2</v>
+      </c>
+      <c r="I7" s="4">
+        <v>1</v>
+      </c>
+      <c r="J7" s="58" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="8" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="F8" s="57" t="s">
+        <v>356</v>
+      </c>
+      <c r="G8" s="4">
+        <v>5</v>
+      </c>
+      <c r="H8" s="4">
+        <v>1</v>
+      </c>
+      <c r="I8" s="4">
+        <v>1</v>
+      </c>
+      <c r="J8" s="58" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="10" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="F10" s="54" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="11" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="F11" s="61" t="s">
+        <v>365</v>
+      </c>
+      <c r="G11" s="59" t="s">
+        <v>366</v>
+      </c>
+      <c r="H11" s="59" t="s">
+        <v>367</v>
+      </c>
+      <c r="I11" s="59" t="s">
+        <v>368</v>
+      </c>
+      <c r="J11" s="59" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="12" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="F12" s="4">
+        <v>260301</v>
+      </c>
+      <c r="G12" s="4">
+        <v>260401</v>
+      </c>
+      <c r="H12" s="47"/>
+      <c r="I12" s="47"/>
+      <c r="J12" s="5" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="13" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="F13" s="4">
+        <v>260201</v>
+      </c>
+      <c r="G13" s="4">
+        <v>260201</v>
+      </c>
+      <c r="H13" s="47"/>
+      <c r="I13" s="47"/>
+      <c r="J13" s="5" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="14" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="F14" s="4">
+        <v>260201</v>
+      </c>
+      <c r="G14" s="4">
+        <v>260201</v>
+      </c>
+      <c r="H14" s="47"/>
+      <c r="I14" s="47"/>
+      <c r="J14" s="5" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="15" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="F15" s="4">
+        <v>200125</v>
+      </c>
+      <c r="G15" s="4">
+        <v>260226</v>
+      </c>
+      <c r="H15" s="47"/>
+      <c r="I15" s="47"/>
+      <c r="J15" s="5" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="16" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="F16" s="56"/>
+      <c r="G16" s="56"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/doc/MAPS_TEST.xlsx
+++ b/doc/MAPS_TEST.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="600" windowWidth="9375" windowHeight="13725" activeTab="5"/>
+    <workbookView xWindow="390" yWindow="600" windowWidth="9375" windowHeight="13725" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="class" sheetId="3" r:id="rId1"/>
@@ -13,13 +13,14 @@
     <sheet name="number_class_details" sheetId="5" r:id="rId4"/>
     <sheet name="조사메뉴" sheetId="6" r:id="rId5"/>
     <sheet name="회원취소건" sheetId="7" r:id="rId6"/>
+    <sheet name="수업회차-물건등록 로직" sheetId="8" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="403">
   <si>
     <t>member_id</t>
   </si>
@@ -1815,6 +1816,148 @@
     <t>비고</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
+  <si>
+    <t>추천</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반 단일 추천건</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>내용</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>수업</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>상태값</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>로딩바구현</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>PT</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>로직</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>순번</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>메뉴</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>수업회차-CLASS</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>수업회차-PT</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>-입찰일정-모달
+-입찰물건관리-상세</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>회원명</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>회원명(수기입력)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>미정</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>만료후 상태값
+(자동변경)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추천으로 변경
+(수기변경)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추천으로 변경
+(등록시 자동변경)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>수기 수정</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>상태값 변경 로직</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>등록시</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>만료시</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>로직없음, 만지지 않음, 있으면 그대로 놔두고 없어도 그대로 놔둠</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>만료 시기</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>시작 시점</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>종목_수업일_회차(더미값자동기재)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>입찰, 취소로 변경 가능, 로딩바 제거됨</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>입찰, 취소로 변경 가능, 로딩바 제거됨
+* 수업회차에 물건탭에도 입찰로 조회 되어야함</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>물건상태-전달완료
+chuchen_date 등록시</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>chuchen_date + 48h</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>수업회차-물건등록시
+(chuchen_date 자동 등록)
+수업회차-물건 삭제시
+(chuchen_date 자동 등록)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>수업의 해당 회차의 2차마감 시간
+(items 시트의 bid_datetime_2 값 활용, 수업회차 물건등록시 자동으로 items 시트에 등록됨)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1826,7 +1969,7 @@
     <numFmt numFmtId="176" formatCode="#,##0_ "/>
     <numFmt numFmtId="177" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2040,8 +2183,16 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2090,8 +2241,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -2140,6 +2297,91 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -5541,7 +5783,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -5713,6 +5955,57 @@
     </xf>
     <xf numFmtId="177" fontId="9" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1136">
@@ -13292,4 +13585,201 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A3:K10"/>
+  <sheetFormatPr defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="63"/>
+    <col min="3" max="3" width="16.5703125" style="63" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.5703125" style="63" customWidth="1"/>
+    <col min="5" max="5" width="25.7109375" style="63" customWidth="1"/>
+    <col min="6" max="6" width="45.7109375" style="63" customWidth="1"/>
+    <col min="7" max="7" width="13.85546875" style="63" customWidth="1"/>
+    <col min="8" max="9" width="30.140625" style="63" customWidth="1"/>
+    <col min="10" max="10" width="26.5703125" style="62" customWidth="1"/>
+    <col min="11" max="11" width="37.5703125" style="62" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.85546875" style="62" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="62"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="74" t="s">
+        <v>378</v>
+      </c>
+      <c r="B3" s="74" t="s">
+        <v>377</v>
+      </c>
+      <c r="C3" s="74" t="s">
+        <v>372</v>
+      </c>
+      <c r="D3" s="74" t="s">
+        <v>379</v>
+      </c>
+      <c r="E3" s="76" t="s">
+        <v>390</v>
+      </c>
+      <c r="F3" s="77"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="71" t="s">
+        <v>383</v>
+      </c>
+      <c r="I3" s="72"/>
+      <c r="J3" s="73" t="s">
+        <v>375</v>
+      </c>
+      <c r="K3" s="73"/>
+    </row>
+    <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="75"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="68" t="s">
+        <v>374</v>
+      </c>
+      <c r="F4" s="68" t="s">
+        <v>389</v>
+      </c>
+      <c r="G4" s="69" t="s">
+        <v>386</v>
+      </c>
+      <c r="H4" s="68" t="s">
+        <v>391</v>
+      </c>
+      <c r="I4" s="70" t="s">
+        <v>392</v>
+      </c>
+      <c r="J4" s="70" t="s">
+        <v>395</v>
+      </c>
+      <c r="K4" s="70" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="64">
+        <v>1</v>
+      </c>
+      <c r="B5" s="64" t="s">
+        <v>370</v>
+      </c>
+      <c r="C5" s="64" t="s">
+        <v>371</v>
+      </c>
+      <c r="D5" s="67" t="s">
+        <v>382</v>
+      </c>
+      <c r="E5" s="66" t="s">
+        <v>387</v>
+      </c>
+      <c r="F5" s="66" t="s">
+        <v>397</v>
+      </c>
+      <c r="G5" s="64" t="s">
+        <v>385</v>
+      </c>
+      <c r="H5" s="64" t="s">
+        <v>384</v>
+      </c>
+      <c r="I5" s="66" t="s">
+        <v>393</v>
+      </c>
+      <c r="J5" s="66" t="s">
+        <v>399</v>
+      </c>
+      <c r="K5" s="65" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="64">
+        <v>2</v>
+      </c>
+      <c r="B6" s="64" t="s">
+        <v>370</v>
+      </c>
+      <c r="C6" s="64" t="s">
+        <v>373</v>
+      </c>
+      <c r="D6" s="64" t="s">
+        <v>380</v>
+      </c>
+      <c r="E6" s="66" t="s">
+        <v>388</v>
+      </c>
+      <c r="F6" s="66" t="s">
+        <v>398</v>
+      </c>
+      <c r="G6" s="64" t="s">
+        <v>385</v>
+      </c>
+      <c r="H6" s="64" t="s">
+        <v>396</v>
+      </c>
+      <c r="I6" s="66" t="s">
+        <v>393</v>
+      </c>
+      <c r="J6" s="66" t="s">
+        <v>401</v>
+      </c>
+      <c r="K6" s="66" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="79.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="64">
+        <v>3</v>
+      </c>
+      <c r="B7" s="64" t="s">
+        <v>370</v>
+      </c>
+      <c r="C7" s="64" t="s">
+        <v>376</v>
+      </c>
+      <c r="D7" s="64" t="s">
+        <v>381</v>
+      </c>
+      <c r="E7" s="66" t="s">
+        <v>388</v>
+      </c>
+      <c r="F7" s="66" t="s">
+        <v>398</v>
+      </c>
+      <c r="G7" s="64" t="s">
+        <v>385</v>
+      </c>
+      <c r="H7" s="64" t="s">
+        <v>396</v>
+      </c>
+      <c r="I7" s="66" t="s">
+        <v>393</v>
+      </c>
+      <c r="J7" s="66" t="s">
+        <v>401</v>
+      </c>
+      <c r="K7" s="66" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C10" s="62"/>
+      <c r="D10" s="62"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:G3"/>
+  </mergeCells>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>